--- a/Sedes_a_priorizar_Juan_Tama_1.xlsx
+++ b/Sedes_a_priorizar_Juan_Tama_1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>219355000291</v>
+        <v>219355000046</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA EL ESCOBAL</t>
+          <t>ESCUELA RURAL MIXTA LOMA ALTA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA GAITANA JUAN TAMA</t>
+          <t>SAN ANDRÉS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,34 +473,6 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>47.0654099137931</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>219355000046</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ESCUELA RURAL MIXTA LOMA ALTA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TIERRA DENTRO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SAN ANDRÉS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>INZA</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
         <v>51.30300603448276</v>
       </c>
     </row>
